--- a/artfynd/A 7459-2026 artfynd.xlsx
+++ b/artfynd/A 7459-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96584900</v>
       </c>
       <c r="B2" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591127.8550244672</v>
+        <v>591127</v>
       </c>
       <c r="R2" t="n">
-        <v>6719551.997489837</v>
+        <v>6719552</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116136627</v>
+        <v>84398760</v>
       </c>
       <c r="B3" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,37 +794,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skräcken (Skräcken), Gstr</t>
+          <t>Långängarna NR, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591111</v>
+        <v>591303</v>
       </c>
       <c r="R3" t="n">
-        <v>6719401</v>
+        <v>6719537</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2020-04-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2020-04-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,33 +866,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Urban Selander</t>
+          <t>Inger Carlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Urban Selander</t>
+          <t>Inger Carlsson, Lotta Delin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116158956</v>
+        <v>126334270</v>
       </c>
       <c r="B4" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,37 +896,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Donken (Donken), Gstr</t>
+          <t>Långängarna, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591048</v>
+        <v>591248</v>
       </c>
       <c r="R4" t="n">
-        <v>6719468</v>
+        <v>6719518</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,22 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,12 +970,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Urban Selander</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Urban Selander</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1015,12 +985,7 @@
         <v>116158963</v>
       </c>
       <c r="B5" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,7 +1013,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Donken (Donken), Gstr</t>
+          <t>Donken, Donken, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1124,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126334270</v>
+        <v>116136627</v>
       </c>
       <c r="B6" t="n">
-        <v>74886</v>
+        <v>58636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,37 +1100,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långängarna, Gstr</t>
+          <t>Skräcken, Skräcken, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591248</v>
+        <v>591111</v>
       </c>
       <c r="R6" t="n">
-        <v>6719518</v>
+        <v>6719401</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,12 +1154,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,15 +1184,122 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Urban Selander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Urban Selander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>116158956</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Donken, Donken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>591048</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6719468</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Urban Selander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Urban Selander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7459-2026 artfynd.xlsx
+++ b/artfynd/A 7459-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96584900</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84398760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126334270</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158963</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116136627</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,8 +1330,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116158956</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>